--- a/my-blog/src/excel/游戏库.xlsx
+++ b/my-blog/src/excel/游戏库.xlsx
@@ -197,7 +197,7 @@
     <t>2_4</t>
   </si>
   <si>
-    <t>策略,角色扮演,卡牌游戏,回合战略,2D,像素,8-bit</t>
+    <t>策略,角色扮演,卡牌,回合制,像素</t>
   </si>
   <si>
     <t>然后，你醒了。冰冷的灯光透过散乱的发丝，在脸颊勾勒出时间的刻痕；脑海中的气泡破碎，只余下飞速消退的碎散浮沫。一切的意义都在溃散。你仍未知晓此地的一切，甚至包括自己在内；只是，仅剩的念头始终在脑海中萦绕，牵扯你迷惘的肉体和灵魂：“今天的治疗快要开始了”</t>
@@ -387,12 +387,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="12"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="14"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -868,7 +868,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -876,9 +876,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1265,40 +1262,40 @@
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="M2" s="1" t="s">
@@ -1312,38 +1309,37 @@
       </c>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3">
+      <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="1">
         <v>2</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="1">
         <v>2</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="1">
         <v>2</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="1">
         <v>2</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="1">
         <v>2</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="1">
         <v>2</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="1">
         <v>2</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="1">
         <v>1</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="1">
         <v>1</v>
       </c>
       <c r="M3" s="1">
@@ -1366,31 +1362,31 @@
       <c r="C4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="1">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="1">
         <v>22</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="1">
         <v>0.9</v>
       </c>
       <c r="M4" s="1" t="s">
@@ -1399,7 +1395,7 @@
       <c r="N4" s="1">
         <v>1</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="4" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1413,38 +1409,37 @@
       <c r="C5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="1">
         <v>2</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
-      <c r="L5" s="3"/>
       <c r="M5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="N5" s="1">
         <v>1</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="4" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1458,37 +1453,37 @@
       <c r="C6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="1">
         <v>3</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="1">
         <v>3</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="1">
         <v>3</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="1">
         <v>3</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="1">
         <v>3</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="1">
         <v>248</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="1">
         <v>0.8</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="O6" s="4" t="s">
         <v>38</v>
       </c>
     </row>

--- a/my-blog/src/excel/游戏库.xlsx
+++ b/my-blog/src/excel/游戏库.xlsx
@@ -38,6 +38,18 @@
       <text>
         <r>
           <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>用，隔开</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <sz val="12"/>
             <rFont val="微软雅黑"/>
             <charset val="134"/>
@@ -46,24 +58,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>用，隔开</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
   <si>
     <t>是否导表</t>
   </si>
@@ -74,6 +74,27 @@
     <t>游戏名</t>
   </si>
   <si>
+    <t>标签组</t>
+  </si>
+  <si>
+    <t>简介</t>
+  </si>
+  <si>
+    <t>原价</t>
+  </si>
+  <si>
+    <t>折扣</t>
+  </si>
+  <si>
+    <t>游戏类型</t>
+  </si>
+  <si>
+    <t>是否推荐</t>
+  </si>
+  <si>
+    <t>发布时间</t>
+  </si>
+  <si>
     <t>大图</t>
   </si>
   <si>
@@ -89,25 +110,22 @@
     <t>小图4</t>
   </si>
   <si>
-    <t>标签组</t>
-  </si>
-  <si>
-    <t>简介</t>
-  </si>
-  <si>
-    <t>原价</t>
-  </si>
-  <si>
-    <t>折扣</t>
-  </si>
-  <si>
-    <t>游戏类型</t>
-  </si>
-  <si>
-    <t>是否推荐</t>
-  </si>
-  <si>
-    <t>发布时间</t>
+    <t>小图5</t>
+  </si>
+  <si>
+    <t>小图6</t>
+  </si>
+  <si>
+    <t>小图7</t>
+  </si>
+  <si>
+    <t>小图8</t>
+  </si>
+  <si>
+    <t>小图9</t>
+  </si>
+  <si>
+    <t>小图10</t>
   </si>
   <si>
     <t>isload</t>
@@ -119,6 +137,27 @@
     <t>name</t>
   </si>
   <si>
+    <t>tag</t>
+  </si>
+  <si>
+    <t>des</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>is_recommended</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
     <t>img_big</t>
   </si>
   <si>
@@ -134,30 +173,39 @@
     <t>img_4</t>
   </si>
   <si>
-    <t>tag</t>
-  </si>
-  <si>
-    <t>des</t>
-  </si>
-  <si>
-    <t>cost</t>
-  </si>
-  <si>
-    <t>count</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>is_recommended</t>
-  </si>
-  <si>
-    <t>time</t>
+    <t>img_5</t>
+  </si>
+  <si>
+    <t>img_6</t>
+  </si>
+  <si>
+    <t>img_7</t>
+  </si>
+  <si>
+    <t>img_8</t>
+  </si>
+  <si>
+    <t>img_9</t>
+  </si>
+  <si>
+    <t>img_10</t>
   </si>
   <si>
     <t>Coser女友的养成方法</t>
   </si>
   <si>
+    <t>galgame,恋爱模拟</t>
+  </si>
+  <si>
+    <t>一款以"和coser女友谈恋爱"为主题的恋爱轻喜剧galgame。在大学毕业前夕，你约了一场cos委托，阴差阳错的收获一个coser女友。在人生的叉路口，你们将走向何方？一段关于青春、成长与爱恋的故事，就此展开。</t>
+  </si>
+  <si>
+    <t>独立</t>
+  </si>
+  <si>
+    <t>2026/7/12 15:00:00</t>
+  </si>
+  <si>
     <t>1_1</t>
   </si>
   <si>
@@ -170,21 +218,18 @@
     <t>1_4</t>
   </si>
   <si>
-    <t>galgame,恋爱模拟</t>
-  </si>
-  <si>
-    <t>一款以"和coser女友谈恋爱"为主题的恋爱轻喜剧galgame。在大学毕业前夕，你约了一场cos委托，阴差阳错的收获一个coser女友。在人生的叉路口，你们将走向何方？一段关于青春、成长与爱恋的故事，就此展开。</t>
-  </si>
-  <si>
-    <t>独立</t>
-  </si>
-  <si>
-    <t>2026/7/12 15:00:00</t>
-  </si>
-  <si>
     <t>病狱</t>
   </si>
   <si>
+    <t>策略,角色扮演,卡牌,回合制,像素</t>
+  </si>
+  <si>
+    <t>然后，你醒了。冰冷的灯光透过散乱的发丝，在脸颊勾勒出时间的刻痕；脑海中的气泡破碎，只余下飞速消退的碎散浮沫。一切的意义都在溃散。你仍未知晓此地的一切，甚至包括自己在内；只是，仅剩的念头始终在脑海中萦绕，牵扯你迷惘的肉体和灵魂：“今天的治疗快要开始了”</t>
+  </si>
+  <si>
+    <t>独立,角色扮演,策略</t>
+  </si>
+  <si>
     <t>2_1</t>
   </si>
   <si>
@@ -195,15 +240,6 @@
   </si>
   <si>
     <t>2_4</t>
-  </si>
-  <si>
-    <t>策略,角色扮演,卡牌,回合制,像素</t>
-  </si>
-  <si>
-    <t>然后，你醒了。冰冷的灯光透过散乱的发丝，在脸颊勾勒出时间的刻痕；脑海中的气泡破碎，只余下飞速消退的碎散浮沫。一切的意义都在溃散。你仍未知晓此地的一切，甚至包括自己在内；只是，仅剩的念头始终在脑海中萦绕，牵扯你迷惘的肉体和灵魂：“今天的治疗快要开始了”</t>
-  </si>
-  <si>
-    <t>独立,角色扮演,策略</t>
   </si>
   <si>
     <t>游戏标题3</t>
@@ -1195,26 +1231,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="29.75" style="1" customWidth="1"/>
-    <col min="4" max="5" width="14.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="28.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.25" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16.625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19.625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="26.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.5" style="1" customWidth="1"/>
+    <col min="11" max="12" width="14.875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="18.5" style="1" customWidth="1"/>
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:21">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1260,55 +1296,91 @@
       <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:21">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:21">
       <c r="B3" s="1">
         <v>1</v>
       </c>
@@ -1322,37 +1394,55 @@
         <v>2</v>
       </c>
       <c r="F3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" s="1">
         <v>2</v>
       </c>
       <c r="I3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="1">
         <v>2</v>
       </c>
       <c r="K3" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="1">
         <v>2</v>
       </c>
       <c r="N3" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" s="1">
         <v>2</v>
       </c>
+      <c r="P3" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>2</v>
+      </c>
+      <c r="R3" s="1">
+        <v>2</v>
+      </c>
+      <c r="S3" s="1">
+        <v>2</v>
+      </c>
+      <c r="T3" s="1">
+        <v>2</v>
+      </c>
+      <c r="U3" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:21">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1360,46 +1450,46 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="1">
+        <v>42</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="1">
+        <v>22</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="1">
         <v>1</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>36</v>
+      <c r="J4" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="K4" s="1">
-        <v>22</v>
-      </c>
-      <c r="L4" s="1">
-        <v>0.9</v>
+        <v>1</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="N4" s="1">
-        <v>1</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>38</v>
+        <v>48</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:21">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1407,43 +1497,43 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="1">
-        <v>2</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>42</v>
+        <v>51</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="N5" s="1">
-        <v>1</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>38</v>
+        <v>56</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:21">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1451,40 +1541,58 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="1">
+        <v>59</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="1">
+        <v>248</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" s="1">
         <v>3</v>
       </c>
-      <c r="E6" s="1">
+      <c r="L6" s="1">
         <v>3</v>
       </c>
-      <c r="F6" s="1">
+      <c r="M6" s="1">
         <v>3</v>
       </c>
-      <c r="G6" s="1">
+      <c r="N6" s="1">
         <v>3</v>
       </c>
-      <c r="H6" s="1">
+      <c r="O6" s="1">
         <v>3</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K6" s="1">
-        <v>248</v>
-      </c>
-      <c r="L6" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>38</v>
+      <c r="P6" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>3</v>
+      </c>
+      <c r="R6" s="1">
+        <v>3</v>
+      </c>
+      <c r="S6" s="1">
+        <v>3</v>
+      </c>
+      <c r="T6" s="1">
+        <v>3</v>
+      </c>
+      <c r="U6" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/my-blog/src/excel/游戏库.xlsx
+++ b/my-blog/src/excel/游戏库.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28500" windowHeight="17535"/>
+    <workbookView windowWidth="28500" windowHeight="17295"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
   <si>
     <t>是否导表</t>
   </si>
@@ -101,31 +101,10 @@
     <t>小图1</t>
   </si>
   <si>
-    <t>小图2</t>
-  </si>
-  <si>
-    <t>小图3</t>
-  </si>
-  <si>
-    <t>小图4</t>
-  </si>
-  <si>
-    <t>小图5</t>
-  </si>
-  <si>
-    <t>小图6</t>
-  </si>
-  <si>
-    <t>小图7</t>
-  </si>
-  <si>
-    <t>小图8</t>
-  </si>
-  <si>
-    <t>小图9</t>
-  </si>
-  <si>
-    <t>小图10</t>
+    <t>开发商</t>
+  </si>
+  <si>
+    <t>发行商</t>
   </si>
   <si>
     <t>isload</t>
@@ -161,97 +140,70 @@
     <t>img_big</t>
   </si>
   <si>
-    <t>img_1</t>
-  </si>
-  <si>
-    <t>img_2</t>
-  </si>
-  <si>
-    <t>img_3</t>
-  </si>
-  <si>
-    <t>img_4</t>
-  </si>
-  <si>
-    <t>img_5</t>
-  </si>
-  <si>
-    <t>img_6</t>
-  </si>
-  <si>
-    <t>img_7</t>
-  </si>
-  <si>
-    <t>img_8</t>
-  </si>
-  <si>
-    <t>img_9</t>
-  </si>
-  <si>
-    <t>img_10</t>
+    <t>img_small</t>
+  </si>
+  <si>
+    <t>developer</t>
+  </si>
+  <si>
+    <t>publisher</t>
   </si>
   <si>
     <t>Coser女友的养成方法</t>
   </si>
   <si>
-    <t>galgame,恋爱模拟</t>
+    <t>{galgame,恋爱模拟}</t>
   </si>
   <si>
     <t>一款以"和coser女友谈恋爱"为主题的恋爱轻喜剧galgame。在大学毕业前夕，你约了一场cos委托，阴差阳错的收获一个coser女友。在人生的叉路口，你们将走向何方？一段关于青春、成长与爱恋的故事，就此展开。</t>
   </si>
   <si>
-    <t>独立</t>
+    <t>{独立}</t>
   </si>
   <si>
     <t>2026/7/12 15:00:00</t>
   </si>
   <si>
-    <t>1_1</t>
-  </si>
-  <si>
-    <t>1_2</t>
-  </si>
-  <si>
-    <t>1_3</t>
-  </si>
-  <si>
-    <t>1_4</t>
+    <t>{1_1,1_2,1_3,1_4}</t>
+  </si>
+  <si>
+    <t>化四级</t>
   </si>
   <si>
     <t>病狱</t>
   </si>
   <si>
-    <t>策略,角色扮演,卡牌,回合制,像素</t>
+    <t>{策略,角色扮演,卡牌,回合制,像素}</t>
   </si>
   <si>
     <t>然后，你醒了。冰冷的灯光透过散乱的发丝，在脸颊勾勒出时间的刻痕；脑海中的气泡破碎，只余下飞速消退的碎散浮沫。一切的意义都在溃散。你仍未知晓此地的一切，甚至包括自己在内；只是，仅剩的念头始终在脑海中萦绕，牵扯你迷惘的肉体和灵魂：“今天的治疗快要开始了”</t>
   </si>
   <si>
-    <t>独立,角色扮演,策略</t>
-  </si>
-  <si>
-    <t>2_1</t>
-  </si>
-  <si>
-    <t>2_2</t>
-  </si>
-  <si>
-    <t>2_3</t>
-  </si>
-  <si>
-    <t>2_4</t>
+    <t>{独立,角色扮演,策略}</t>
+  </si>
+  <si>
+    <t>{2_1,2_2,2_3,2_4}</t>
+  </si>
+  <si>
+    <t>黑岩</t>
   </si>
   <si>
     <t>游戏标题3</t>
   </si>
   <si>
-    <t>标签1,标签4,标签5</t>
+    <t>{标签1,标签4,标签5}</t>
   </si>
   <si>
     <t>这里是游戏简介3</t>
   </si>
   <si>
-    <t>策略</t>
+    <t>{策略}</t>
+  </si>
+  <si>
+    <t>{1_1,1_2,1_3,1_4,2_1,2_2,2_3,2_4}</t>
+  </si>
+  <si>
+    <t>小克</t>
   </si>
 </sst>
 </file>
@@ -1231,26 +1183,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="29.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="26.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="56.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="70.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="40.125" style="1" customWidth="1"/>
     <col min="9" max="9" width="19.625" style="1" customWidth="1"/>
     <col min="10" max="10" width="26.5" style="1" customWidth="1"/>
-    <col min="11" max="12" width="14.875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.75" style="1" customWidth="1"/>
-    <col min="15" max="15" width="18.5" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="11" max="11" width="14.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="40.375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="22.375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="25.125" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1293,94 +1245,52 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="H2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:14">
       <c r="B3" s="1">
         <v>1</v>
       </c>
@@ -1420,29 +1330,8 @@
       <c r="N3" s="1">
         <v>2</v>
       </c>
-      <c r="O3" s="1">
-        <v>2</v>
-      </c>
-      <c r="P3" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>2</v>
-      </c>
-      <c r="R3" s="1">
-        <v>2</v>
-      </c>
-      <c r="S3" s="1">
-        <v>2</v>
-      </c>
-      <c r="T3" s="1">
-        <v>2</v>
-      </c>
-      <c r="U3" s="1">
-        <v>2</v>
-      </c>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:14">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1450,13 +1339,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="F4" s="1">
         <v>22</v>
@@ -1465,31 +1354,28 @@
         <v>0.9</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:14">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1497,43 +1383,40 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="K5" s="1">
         <v>2</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:14">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1541,13 +1424,13 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="F6" s="1">
         <v>248</v>
@@ -1556,43 +1439,22 @@
         <v>0.8</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="K6" s="1">
         <v>3</v>
       </c>
-      <c r="L6" s="1">
-        <v>3</v>
-      </c>
-      <c r="M6" s="1">
-        <v>3</v>
-      </c>
-      <c r="N6" s="1">
-        <v>3</v>
-      </c>
-      <c r="O6" s="1">
-        <v>3</v>
-      </c>
-      <c r="P6" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>3</v>
-      </c>
-      <c r="R6" s="1">
-        <v>3</v>
-      </c>
-      <c r="S6" s="1">
-        <v>3</v>
-      </c>
-      <c r="T6" s="1">
-        <v>3</v>
-      </c>
-      <c r="U6" s="1">
-        <v>3</v>
+      <c r="L6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
